--- a/Medisure/USER_DOCS.xlsx
+++ b/Medisure/USER_DOCS.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col width="62.85546875" customWidth="1" style="1" min="2" max="2"/>
@@ -518,133 +518,48 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>Terry</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>1234</v>
+          <t>katy</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>$2b$12$ATNPDwBcu/irjK8qttoTQeB0DDiBh9C3sFQhX3XS326Z9/buKQVmG</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>보령아스트릭스캡슐100밀리그람(아스피린)</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>캐롤시럽(이부프로펜)</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>tom</t>
+          <t>terry</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>$2b$12$DQ4Gk33rj7JsVAnRMxjNteLV95Xls46SvG3HipZu8n3s1Q5.MAuvS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>alice</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>$2b$12$8Zv15CpU1kdINnvGlVIT0egcklggjMr1E9u/d/YJxzBHlimRGpng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>nero</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>$2b$12$fZkKyhUHvSDyh5y9W1FEZ.AGQ2HiE/Q6vgb.ATRRzyrn/x.HtIl/i</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>ted</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>$2b$12$qKlriWXZbiugT98v/5NyBOXyR3T/Mhq0/dAuQOe58YI8dvFoWMsA2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>rora</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>$2b$12$hVtn3og1ukwfZVwKAUAzSusi1eEnkPRvFuHdQIWE25vBdD5VDevmi</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>sadie</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>$2b$12$OBSHGZnCPUM27I37PBJqsusZcPQTNNLwCe5IucIEzM3qzwseyLuOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>$2b$12$h1Ygs3eLpli4R0/L2hALaunSVXrEGORTvpTlF/GYQU/e0tesKFDwG</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>gr</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>$2b$12$5QxYnZRddOVWvoZdpe6Fk.vd8NxI3JqFiC8tLuuehjc26qOCYoeMu</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>katy</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>$2b$12$ATNPDwBcu/irjK8qttoTQeB0DDiBh9C3sFQhX3XS326Z9/buKQVmG</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>보령아스트릭스캡슐100밀리그람(아스피린)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>캐롤시럽(이부프로펜)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="0" t="n"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tom</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$2b$12$r1P7rTIVDla0n4SWYddL3OoVoKkFx8BbjmLUCUKP5qDubDvhsNcFe</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
